--- a/data/ready_stocks/tt-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/tt-wb-stocks-updated.xlsx
@@ -612,7 +612,7 @@
         <v>2050157477840</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -628,7 +628,7 @@
         <v>2050152591763</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -652,7 +652,7 @@
         <v>2050152591596</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -668,7 +668,7 @@
         <v>2050152592258</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -676,7 +676,7 @@
         <v>2050152591992</v>
       </c>
       <c r="B35">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -684,7 +684,7 @@
         <v>2050152591886</v>
       </c>
       <c r="B36">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -692,7 +692,7 @@
         <v>2050152592340</v>
       </c>
       <c r="B37">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
